--- a/lecNote/09_Project/etc/프로젝트관리1.xlsx
+++ b/lecNote/09_Project/etc/프로젝트관리1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EZ\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\09_Project\etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6CCFBC1-B549-479C-B0B3-7DDD1C8F4497}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE5D8F4-AD9A-4F68-AD51-407570AA16B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -52,46 +52,13 @@
     <t>공동작업</t>
   </si>
   <si>
-    <t>주제에 대한 feature 확인</t>
-  </si>
-  <si>
     <t>데이터 확보 계획 수립</t>
   </si>
   <si>
-    <t>데이터 수집과 정리</t>
-  </si>
-  <si>
     <t>▼</t>
   </si>
   <si>
-    <t>서울시 열린데이터광장 데이터</t>
-  </si>
-  <si>
-    <t>기상청 데이터</t>
-  </si>
-  <si>
-    <t>공공데이터포털 데이터</t>
-  </si>
-  <si>
-    <t>통계청 데이터</t>
-  </si>
-  <si>
-    <t>수집데이터 DB 적재</t>
-  </si>
-  <si>
-    <t>연구 모형 및 조사 설계</t>
-  </si>
-  <si>
     <t>데이터 특성 확인 분석</t>
-  </si>
-  <si>
-    <t>데이터 전처리</t>
-  </si>
-  <si>
-    <t>공공자전거 대여량 예측 모델</t>
-  </si>
-  <si>
-    <t>민간PM 수요 예측 모델</t>
   </si>
   <si>
     <t>완성 모델 서비스화</t>
@@ -187,11 +154,6 @@
     <t>10월10일</t>
   </si>
   <si>
-    <t>9월 28일~30일
-데이터 수집과 정리</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>10월 1일~5일
 연구 모형 및 조사 설계</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -199,6 +161,74 @@
   <si>
     <t>10월 6일~10일
 완성 모델 서비스화</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>민간 수요 예측 모델</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>상권분석 예측 모델</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>주제에 대한 feature 추출</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>수집데이터 DB 적재</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">프로젝트명
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>(2026.09.23~2026.10.12)</t>
+    </r>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>XXX 데이터 / ooo 데이터 정리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>공공데이터포털 데이터 정리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>국토교통부 데이터 정리</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>인사이트 도출을 위한 시각화</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">9월 28일~30일
+데이터 수집과 </t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이터 수집과 전처리, 인사이트 도출</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>예측 모형 설계 및 구현</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -206,7 +236,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -260,8 +290,41 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Carlito"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -281,11 +344,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6F4D7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3F5F7"/>
       </patternFill>
     </fill>
     <fill>
@@ -310,11 +368,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA7AAAD"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFF6F7F8"/>
       </patternFill>
     </fill>
@@ -323,8 +376,14 @@
         <fgColor rgb="FFA8BDD3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -508,12 +567,38 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF111111"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF111111"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF111111"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF111111"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF111111"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF111111"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -527,14 +612,71 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -548,64 +690,16 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -821,245 +915,165 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W39"/>
+  <dimension ref="B2:X45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="25.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="17" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.375" customWidth="1"/>
-    <col min="19" max="19" width="1.5" customWidth="1"/>
-    <col min="20" max="23" width="7" customWidth="1"/>
+    <col min="1" max="1" width="2.625" customWidth="1"/>
+    <col min="2" max="2" width="25.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="18" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="6.375" customWidth="1"/>
+    <col min="20" max="20" width="1.5" customWidth="1"/>
+    <col min="21" max="24" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="18" customHeight="1">
-      <c r="A1" s="2" t="s">
+    <row r="2" spans="2:24" ht="17.25" customHeight="1">
+      <c r="B2" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="26"/>
+      <c r="N2" s="26"/>
+      <c r="O2" s="26"/>
+      <c r="P2" s="26"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="26"/>
+      <c r="S2" s="26"/>
+    </row>
+    <row r="3" spans="2:24" ht="21" customHeight="1">
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="26"/>
+      <c r="G3" s="26"/>
+      <c r="H3" s="26"/>
+      <c r="I3" s="26"/>
+      <c r="J3" s="26"/>
+      <c r="K3" s="26"/>
+      <c r="L3" s="26"/>
+      <c r="M3" s="26"/>
+      <c r="N3" s="26"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="26"/>
+      <c r="Q3" s="26"/>
+      <c r="R3" s="26"/>
+      <c r="S3" s="26"/>
+    </row>
+    <row r="5" spans="2:24" ht="18" customHeight="1">
+      <c r="B5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="K5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="1"/>
-      <c r="U1" s="1"/>
-      <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-    </row>
-    <row r="2" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A2" s="12" t="s">
+      <c r="S5" s="2"/>
+      <c r="T5" s="1"/>
+      <c r="U5" s="1"/>
+      <c r="V5" s="1"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
+    </row>
+    <row r="6" spans="2:24" ht="15.75" customHeight="1">
+      <c r="B6" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="13"/>
-      <c r="K2" s="13"/>
-      <c r="L2" s="13"/>
-      <c r="M2" s="13"/>
-      <c r="N2" s="13"/>
-      <c r="O2" s="13"/>
-      <c r="P2" s="13"/>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="14"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="8" t="s">
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
+      <c r="J6" s="10"/>
+      <c r="K6" s="10"/>
+      <c r="L6" s="10"/>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="1"/>
+      <c r="U6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="U2" s="9"/>
-      <c r="V2" s="10" t="s">
+      <c r="V6" s="28"/>
+      <c r="W6" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="W2" s="11"/>
-    </row>
-    <row r="3" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A3" s="15" t="s">
+      <c r="X6" s="30"/>
+    </row>
+    <row r="7" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-      <c r="S3" s="1"/>
-      <c r="T3" s="1"/>
-      <c r="U3" s="1"/>
-      <c r="V3" s="1"/>
-      <c r="W3" s="1"/>
-    </row>
-    <row r="4" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A4" s="15"/>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="1"/>
-      <c r="T4" s="23" t="s">
-        <v>36</v>
-      </c>
-      <c r="U4" s="24"/>
-      <c r="V4" s="24"/>
-      <c r="W4" s="25"/>
-    </row>
-    <row r="5" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A5" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="26"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="28"/>
-    </row>
-    <row r="6" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="26"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="28"/>
-    </row>
-    <row r="7" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="3"/>
       <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
@@ -1072,21 +1086,21 @@
       <c r="Q7" s="1"/>
       <c r="R7" s="1"/>
       <c r="S7" s="1"/>
-      <c r="T7" s="26"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27"/>
-      <c r="W7" s="28"/>
-    </row>
-    <row r="8" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="6" t="s">
+      <c r="T7" s="1"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+    </row>
+    <row r="8" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B8" s="8"/>
+      <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
+      <c r="D8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1101,55 +1115,57 @@
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
-      <c r="T8" s="29"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="31"/>
-    </row>
-    <row r="9" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A9" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="14"/>
+      <c r="T8" s="1"/>
+      <c r="U8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="14"/>
+    </row>
+    <row r="9" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="V9" s="20"/>
-      <c r="W9" s="1"/>
-    </row>
-    <row r="10" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A10" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D10" s="1"/>
+      <c r="U9" s="15"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="16"/>
+      <c r="X9" s="17"/>
+    </row>
+    <row r="10" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B10" s="8"/>
+      <c r="C10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
@@ -1162,23 +1178,25 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="21"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="1"/>
-    </row>
-    <row r="11" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A11" s="15"/>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D11" s="1"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="16"/>
+      <c r="W10" s="16"/>
+      <c r="X10" s="17"/>
+    </row>
+    <row r="11" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B11" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="3"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
@@ -1191,25 +1209,23 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
-      <c r="V11" s="1"/>
-      <c r="W11" s="1"/>
-    </row>
-    <row r="12" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A12" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D12" s="1"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="16"/>
+      <c r="W11" s="16"/>
+      <c r="X11" s="17"/>
+    </row>
+    <row r="12" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B12" s="8"/>
+      <c r="C12" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -1221,53 +1237,51 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
-      <c r="T12" s="23" t="s">
-        <v>50</v>
-      </c>
-      <c r="U12" s="24"/>
-      <c r="V12" s="24"/>
-      <c r="W12" s="25"/>
-    </row>
-    <row r="13" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A13" s="15"/>
-      <c r="B13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="27"/>
-      <c r="V13" s="27"/>
-      <c r="W13" s="28"/>
-    </row>
-    <row r="14" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" s="6" t="s">
+      <c r="T12" s="1"/>
+      <c r="U12" s="18"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="20"/>
+    </row>
+    <row r="13" spans="2:24" ht="15.75" customHeight="1">
+      <c r="B13" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="11"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+      <c r="V13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="W13" s="22"/>
+      <c r="X13" s="1"/>
+    </row>
+    <row r="14" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B14" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1283,25 +1297,25 @@
       <c r="Q14" s="1"/>
       <c r="R14" s="1"/>
       <c r="S14" s="1"/>
-      <c r="T14" s="26"/>
-      <c r="U14" s="27"/>
-      <c r="V14" s="27"/>
-      <c r="W14" s="28"/>
-    </row>
-    <row r="15" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A15" s="15"/>
-      <c r="B15" s="6" t="s">
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+      <c r="V14" s="23"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="1"/>
+    </row>
+    <row r="15" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B15" s="8"/>
+      <c r="C15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="4"/>
-      <c r="I15" s="1"/>
+      <c r="I15" s="4"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1312,22 +1326,22 @@
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
       <c r="S15" s="1"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="27"/>
-      <c r="V15" s="27"/>
-      <c r="W15" s="28"/>
-    </row>
-    <row r="16" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A16" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+    </row>
+    <row r="16" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B16" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
@@ -1343,25 +1357,27 @@
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
-      <c r="T16" s="29"/>
-      <c r="U16" s="30"/>
-      <c r="V16" s="30"/>
-      <c r="W16" s="31"/>
-    </row>
-    <row r="17" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A17" s="15"/>
-      <c r="B17" s="6" t="s">
+      <c r="T16" s="1"/>
+      <c r="U16" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="V16" s="13"/>
+      <c r="W16" s="13"/>
+      <c r="X16" s="14"/>
+    </row>
+    <row r="17" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B17" s="8"/>
+      <c r="C17" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="H17" s="4"/>
-      <c r="I17" s="1"/>
+      <c r="I17" s="4"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1373,27 +1389,27 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
-      <c r="V17" s="1"/>
-      <c r="W17" s="1"/>
-    </row>
-    <row r="18" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A18" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="6" t="s">
+      <c r="U17" s="15"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="17"/>
+    </row>
+    <row r="18" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B18" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="1"/>
       <c r="I18" s="3"/>
-      <c r="J18" s="1"/>
+      <c r="J18" s="3"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
@@ -1404,21 +1420,19 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="V18" s="20"/>
-      <c r="W18" s="1"/>
-    </row>
-    <row r="19" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A19" s="15"/>
-      <c r="B19" s="6" t="s">
+      <c r="U18" s="15"/>
+      <c r="V18" s="16"/>
+      <c r="W18" s="16"/>
+      <c r="X18" s="17"/>
+    </row>
+    <row r="19" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B19" s="8"/>
+      <c r="C19" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1435,53 +1449,55 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="22"/>
-      <c r="W19" s="1"/>
-    </row>
-    <row r="20" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A20" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="13"/>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
-      <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="13"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="13"/>
-      <c r="R20" s="14"/>
+      <c r="U19" s="15"/>
+      <c r="V19" s="16"/>
+      <c r="W19" s="16"/>
+      <c r="X19" s="17"/>
+    </row>
+    <row r="20" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1"/>
-    </row>
-    <row r="21" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A21" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D21" s="1"/>
+      <c r="U20" s="18"/>
+      <c r="V20" s="19"/>
+      <c r="W20" s="19"/>
+      <c r="X20" s="20"/>
+    </row>
+    <row r="21" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B21" s="8"/>
+      <c r="C21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="4"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1492,28 +1508,28 @@
       <c r="Q21" s="1"/>
       <c r="R21" s="1"/>
       <c r="S21" s="1"/>
-      <c r="T21" s="23" t="s">
-        <v>51</v>
-      </c>
-      <c r="U21" s="24"/>
-      <c r="V21" s="24"/>
-      <c r="W21" s="25"/>
-    </row>
-    <row r="22" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A22" s="15"/>
-      <c r="B22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D22" s="1"/>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+    </row>
+    <row r="22" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B22" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
@@ -1523,28 +1539,28 @@
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
       <c r="S22" s="1"/>
-      <c r="T22" s="26"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="27"/>
-      <c r="W22" s="28"/>
-    </row>
-    <row r="23" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A23" s="15" t="s">
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="W22" s="22"/>
+      <c r="X22" s="1"/>
+    </row>
+    <row r="23" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B23" s="8"/>
+      <c r="C23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="1"/>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
@@ -1554,59 +1570,57 @@
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="26"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="27"/>
-      <c r="W23" s="28"/>
-    </row>
-    <row r="24" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A24" s="15"/>
-      <c r="B24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="27"/>
-      <c r="V24" s="27"/>
-      <c r="W24" s="28"/>
-    </row>
-    <row r="25" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A25" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="6" t="s">
+      <c r="T23" s="1"/>
+      <c r="U23" s="1"/>
+      <c r="V23" s="23"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="1"/>
+    </row>
+    <row r="24" spans="2:24" ht="15.75" customHeight="1">
+      <c r="B24" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
+      <c r="P24" s="10"/>
+      <c r="Q24" s="10"/>
+      <c r="R24" s="10"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+    </row>
+    <row r="25" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D25" s="1"/>
+      <c r="D25" s="5" t="s">
+        <v>21</v>
+      </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
+      <c r="I25" s="3"/>
       <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
@@ -1614,20 +1628,22 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="30"/>
-      <c r="V25" s="30"/>
-      <c r="W25" s="31"/>
-    </row>
-    <row r="26" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A26" s="15"/>
-      <c r="B26" s="6" t="s">
+      <c r="T25" s="1"/>
+      <c r="U25" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="14"/>
+    </row>
+    <row r="26" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B26" s="8"/>
+      <c r="C26" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C26" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="1"/>
+      <c r="D26" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
@@ -1635,8 +1651,8 @@
       <c r="I26" s="1"/>
       <c r="J26" s="4"/>
       <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
@@ -1644,201 +1660,189 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
-      <c r="V26" s="1"/>
-      <c r="W26" s="1"/>
-    </row>
-    <row r="27" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A27" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="6" t="s">
+      <c r="U26" s="15"/>
+      <c r="V26" s="16"/>
+      <c r="W26" s="16"/>
+      <c r="X26" s="17"/>
+    </row>
+    <row r="27" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B27" s="33"/>
+      <c r="C27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="1"/>
+      <c r="D27" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="V27" s="20"/>
-      <c r="W27" s="1"/>
-    </row>
-    <row r="28" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A28" s="15"/>
-      <c r="B28" s="6" t="s">
+      <c r="U27" s="15"/>
+      <c r="V27" s="16"/>
+      <c r="W27" s="16"/>
+      <c r="X27" s="17"/>
+    </row>
+    <row r="28" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B28" s="34"/>
+      <c r="C28" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D28" s="1"/>
+      <c r="D28" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
       <c r="L28" s="1"/>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="21"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="1"/>
-    </row>
-    <row r="29" spans="1:23" ht="15.75" customHeight="1">
-      <c r="A29" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
-      <c r="K29" s="13"/>
-      <c r="L29" s="13"/>
-      <c r="M29" s="13"/>
-      <c r="N29" s="13"/>
-      <c r="O29" s="13"/>
-      <c r="P29" s="13"/>
-      <c r="Q29" s="13"/>
-      <c r="R29" s="14"/>
+      <c r="U28" s="15"/>
+      <c r="V28" s="16"/>
+      <c r="W28" s="16"/>
+      <c r="X28" s="17"/>
+    </row>
+    <row r="29" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B29" s="31"/>
+      <c r="C29" s="6"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="1"/>
-      <c r="V29" s="1"/>
-      <c r="W29" s="1"/>
-    </row>
-    <row r="30" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A30" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D30" s="1"/>
+      <c r="U29" s="15"/>
+      <c r="V29" s="16"/>
+      <c r="W29" s="16"/>
+      <c r="X29" s="17"/>
+    </row>
+    <row r="30" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B30" s="32"/>
+      <c r="C30" s="6"/>
+      <c r="D30" s="7"/>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30" s="3"/>
-      <c r="O30" s="3"/>
-      <c r="P30" s="3"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
-      <c r="T30" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="U30" s="24"/>
-      <c r="V30" s="24"/>
-      <c r="W30" s="25"/>
-    </row>
-    <row r="31" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A31" s="15"/>
-      <c r="B31" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="D31" s="1"/>
+      <c r="T30" s="1"/>
+      <c r="U30" s="15"/>
+      <c r="V30" s="16"/>
+      <c r="W30" s="16"/>
+      <c r="X30" s="17"/>
+    </row>
+    <row r="31" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B31" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="E31" s="1"/>
       <c r="F31" s="1"/>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
-      <c r="T31" s="26"/>
-      <c r="U31" s="27"/>
-      <c r="V31" s="27"/>
-      <c r="W31" s="28"/>
-    </row>
-    <row r="32" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A32" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D32" s="1"/>
+      <c r="T31" s="1"/>
+      <c r="U31" s="18"/>
+      <c r="V31" s="19"/>
+      <c r="W31" s="19"/>
+      <c r="X31" s="20"/>
+    </row>
+    <row r="32" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B32" s="8"/>
+      <c r="C32" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
       <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+      <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
-      <c r="T32" s="26"/>
-      <c r="U32" s="27"/>
-      <c r="V32" s="27"/>
-      <c r="W32" s="28"/>
-    </row>
-    <row r="33" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A33" s="15"/>
-      <c r="B33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D33" s="1"/>
+      <c r="T32" s="1"/>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
+      <c r="W32" s="1"/>
+      <c r="X32" s="1"/>
+    </row>
+    <row r="33" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B33" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>22</v>
+      </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
@@ -1848,28 +1852,28 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
+      <c r="N33" s="3"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="1"/>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
-      <c r="T33" s="26"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="27"/>
-      <c r="W33" s="28"/>
-    </row>
-    <row r="34" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A34" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C34" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D34" s="1"/>
+      <c r="T33" s="1"/>
+      <c r="U33" s="1"/>
+      <c r="V33" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="W33" s="22"/>
+      <c r="X33" s="1"/>
+    </row>
+    <row r="34" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B34" s="8"/>
+      <c r="C34" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1879,57 +1883,55 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
-      <c r="T34" s="29"/>
-      <c r="U34" s="30"/>
-      <c r="V34" s="30"/>
-      <c r="W34" s="31"/>
-    </row>
-    <row r="35" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A35" s="15"/>
-      <c r="B35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="1"/>
-      <c r="S35" s="1"/>
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="23"/>
+      <c r="W34" s="24"/>
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" spans="2:24" ht="15.75" customHeight="1">
+      <c r="B35" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="10"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
+      <c r="J35" s="10"/>
+      <c r="K35" s="10"/>
+      <c r="L35" s="10"/>
+      <c r="M35" s="10"/>
+      <c r="N35" s="10"/>
+      <c r="O35" s="10"/>
+      <c r="P35" s="10"/>
+      <c r="Q35" s="10"/>
+      <c r="R35" s="10"/>
+      <c r="S35" s="11"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
       <c r="W35" s="1"/>
-    </row>
-    <row r="36" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A36" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="B36" s="6" t="s">
+      <c r="X35" s="1"/>
+    </row>
+    <row r="36" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="D36" s="1"/>
+      <c r="D36" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
@@ -1939,26 +1941,28 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="N36" s="3"/>
+      <c r="N36" s="1"/>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="1"/>
+      <c r="Q36" s="3"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="1"/>
-      <c r="V36" s="1"/>
-      <c r="W36" s="1"/>
-    </row>
-    <row r="37" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A37" s="15"/>
-      <c r="B37" s="6" t="s">
+      <c r="U36" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="14"/>
+    </row>
+    <row r="37" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B37" s="8"/>
+      <c r="C37" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="1"/>
+      <c r="D37" s="7" t="s">
+        <v>23</v>
+      </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
@@ -1967,50 +1971,58 @@
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
       <c r="O37" s="4"/>
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
-      <c r="V37" s="1"/>
-      <c r="W37" s="1"/>
-    </row>
-    <row r="38" spans="1:23" ht="14.25" customHeight="1">
-      <c r="A38" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
-      <c r="H38" s="17"/>
-      <c r="I38" s="17"/>
-      <c r="J38" s="17"/>
-      <c r="K38" s="17"/>
-      <c r="L38" s="17"/>
-      <c r="M38" s="17"/>
-      <c r="N38" s="17"/>
-      <c r="O38" s="17"/>
-      <c r="P38" s="17"/>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="18"/>
+      <c r="U37" s="15"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="17"/>
+    </row>
+    <row r="38" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B38" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="3"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
-      <c r="U38" s="1"/>
-      <c r="V38" s="1"/>
-      <c r="W38" s="1"/>
-    </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
+      <c r="U38" s="15"/>
+      <c r="V38" s="16"/>
+      <c r="W38" s="16"/>
+      <c r="X38" s="17"/>
+    </row>
+    <row r="39" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B39" s="8"/>
+      <c r="C39" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>22</v>
+      </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
@@ -2021,48 +2033,222 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
+      <c r="O39" s="4"/>
+      <c r="P39" s="4"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="1"/>
-      <c r="V39" s="1"/>
-      <c r="W39" s="1"/>
+      <c r="U39" s="15"/>
+      <c r="V39" s="16"/>
+      <c r="W39" s="16"/>
+      <c r="X39" s="17"/>
+    </row>
+    <row r="40" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B40" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="1"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="19"/>
+      <c r="W40" s="19"/>
+      <c r="X40" s="20"/>
+    </row>
+    <row r="41" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B41" s="8"/>
+      <c r="C41" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" s="1"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="1"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
+      <c r="P41" s="4"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="1"/>
+      <c r="U41" s="1"/>
+      <c r="V41" s="1"/>
+      <c r="W41" s="1"/>
+      <c r="X41" s="1"/>
+    </row>
+    <row r="42" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B42" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="O42" s="3"/>
+      <c r="P42" s="3"/>
+      <c r="Q42" s="3"/>
+      <c r="R42" s="1"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="1"/>
+      <c r="U42" s="1"/>
+      <c r="V42" s="1"/>
+      <c r="W42" s="1"/>
+      <c r="X42" s="1"/>
+    </row>
+    <row r="43" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B43" s="8"/>
+      <c r="C43" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="1"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
+      <c r="P43" s="4"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="1"/>
+      <c r="U43" s="1"/>
+      <c r="V43" s="1"/>
+      <c r="W43" s="1"/>
+      <c r="X43" s="1"/>
+    </row>
+    <row r="44" spans="2:24" ht="14.25" customHeight="1">
+      <c r="B44" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="10"/>
+      <c r="G44" s="10"/>
+      <c r="H44" s="10"/>
+      <c r="I44" s="10"/>
+      <c r="J44" s="10"/>
+      <c r="K44" s="10"/>
+      <c r="L44" s="10"/>
+      <c r="M44" s="10"/>
+      <c r="N44" s="10"/>
+      <c r="O44" s="10"/>
+      <c r="P44" s="10"/>
+      <c r="Q44" s="10"/>
+      <c r="R44" s="10"/>
+      <c r="S44" s="11"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
+      <c r="W44" s="1"/>
+      <c r="X44" s="1"/>
+    </row>
+    <row r="45" spans="2:24">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="J45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="O45" s="1"/>
+      <c r="P45" s="1"/>
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
+      <c r="W45" s="1"/>
+      <c r="X45" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="A38:R38"/>
-    <mergeCell ref="T4:W8"/>
-    <mergeCell ref="T12:W16"/>
-    <mergeCell ref="T21:W25"/>
-    <mergeCell ref="T30:W34"/>
-    <mergeCell ref="U9:V10"/>
-    <mergeCell ref="U18:V19"/>
-    <mergeCell ref="U27:V28"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A29:R29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A18:A19"/>
-    <mergeCell ref="A20:R20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="A23:A24"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="A9:R9"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="V2:W2"/>
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
+  <mergeCells count="31">
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B2:S3"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="B6:S6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:S24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:S13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="B42:B43"/>
+    <mergeCell ref="B44:S44"/>
+    <mergeCell ref="U8:X12"/>
+    <mergeCell ref="U16:X20"/>
+    <mergeCell ref="U25:X31"/>
+    <mergeCell ref="U36:X40"/>
+    <mergeCell ref="V13:W14"/>
+    <mergeCell ref="V22:W23"/>
+    <mergeCell ref="V33:W34"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="B35:S35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B20:B21"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/lecNote/09_Project/etc/프로젝트관리1.xlsx
+++ b/lecNote/09_Project/etc/프로젝트관리1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ai\lecNote\09_Project\etc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DE5D8F4-AD9A-4F68-AD51-407570AA16B9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFBD2FE1-7F6D-4378-BC16-4731ABB2FAA0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -621,55 +621,16 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -690,16 +651,55 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -930,46 +930,46 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="17.25" customHeight="1">
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
-      <c r="K2" s="26"/>
-      <c r="L2" s="26"/>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
     </row>
     <row r="3" spans="2:24" ht="21" customHeight="1">
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="26"/>
-      <c r="L3" s="26"/>
-      <c r="M3" s="26"/>
-      <c r="N3" s="26"/>
-      <c r="O3" s="26"/>
-      <c r="P3" s="26"/>
-      <c r="Q3" s="26"/>
-      <c r="R3" s="26"/>
-      <c r="S3" s="26"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
     </row>
     <row r="5" spans="2:24" ht="18" customHeight="1">
       <c r="B5" s="2" t="s">
@@ -1031,38 +1031,38 @@
       <c r="X5" s="1"/>
     </row>
     <row r="6" spans="2:24" ht="15.75" customHeight="1">
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="11"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
+      <c r="O6" s="19"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="19"/>
+      <c r="R6" s="19"/>
+      <c r="S6" s="20"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="27" t="s">
+      <c r="U6" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="V6" s="28"/>
-      <c r="W6" s="29" t="s">
+      <c r="V6" s="15"/>
+      <c r="W6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="X6" s="30"/>
+      <c r="X6" s="17"/>
     </row>
     <row r="7" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="21" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -1093,7 +1093,7 @@
       <c r="X7" s="1"/>
     </row>
     <row r="8" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B8" s="8"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="6" t="s">
         <v>8</v>
       </c>
@@ -1116,15 +1116,15 @@
       <c r="R8" s="1"/>
       <c r="S8" s="1"/>
       <c r="T8" s="1"/>
-      <c r="U8" s="12" t="s">
+      <c r="U8" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="V8" s="13"/>
-      <c r="W8" s="13"/>
-      <c r="X8" s="14"/>
+      <c r="V8" s="23"/>
+      <c r="W8" s="23"/>
+      <c r="X8" s="24"/>
     </row>
     <row r="9" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -1149,13 +1149,13 @@
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
-      <c r="U9" s="15"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="17"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="26"/>
+      <c r="W9" s="26"/>
+      <c r="X9" s="27"/>
     </row>
     <row r="10" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B10" s="8"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="6" t="s">
         <v>8</v>
       </c>
@@ -1178,13 +1178,13 @@
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
-      <c r="U10" s="15"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="17"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="26"/>
+      <c r="W10" s="26"/>
+      <c r="X10" s="27"/>
     </row>
     <row r="11" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="21" t="s">
         <v>10</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1209,13 +1209,13 @@
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="17"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="26"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="27"/>
     </row>
     <row r="12" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B12" s="8"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="6" t="s">
         <v>8</v>
       </c>
@@ -1238,42 +1238,42 @@
       <c r="R12" s="1"/>
       <c r="S12" s="1"/>
       <c r="T12" s="1"/>
-      <c r="U12" s="18"/>
-      <c r="V12" s="19"/>
-      <c r="W12" s="19"/>
-      <c r="X12" s="20"/>
+      <c r="U12" s="28"/>
+      <c r="V12" s="29"/>
+      <c r="W12" s="29"/>
+      <c r="X12" s="30"/>
     </row>
     <row r="13" spans="2:24" ht="15.75" customHeight="1">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="11"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="20"/>
       <c r="T13" s="1"/>
       <c r="U13" s="1"/>
-      <c r="V13" s="21" t="s">
+      <c r="V13" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="W13" s="22"/>
+      <c r="W13" s="32"/>
       <c r="X13" s="1"/>
     </row>
     <row r="14" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="21" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="6" t="s">
@@ -1299,12 +1299,12 @@
       <c r="S14" s="1"/>
       <c r="T14" s="1"/>
       <c r="U14" s="1"/>
-      <c r="V14" s="23"/>
-      <c r="W14" s="24"/>
+      <c r="V14" s="33"/>
+      <c r="W14" s="34"/>
       <c r="X14" s="1"/>
     </row>
     <row r="15" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B15" s="8"/>
+      <c r="B15" s="21"/>
       <c r="C15" s="6" t="s">
         <v>8</v>
       </c>
@@ -1333,7 +1333,7 @@
       <c r="X15" s="1"/>
     </row>
     <row r="16" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="21" t="s">
         <v>47</v>
       </c>
       <c r="C16" s="6" t="s">
@@ -1358,15 +1358,15 @@
       <c r="R16" s="1"/>
       <c r="S16" s="1"/>
       <c r="T16" s="1"/>
-      <c r="U16" s="12" t="s">
+      <c r="U16" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="V16" s="13"/>
-      <c r="W16" s="13"/>
-      <c r="X16" s="14"/>
+      <c r="V16" s="23"/>
+      <c r="W16" s="23"/>
+      <c r="X16" s="24"/>
     </row>
     <row r="17" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B17" s="8"/>
+      <c r="B17" s="21"/>
       <c r="C17" s="6" t="s">
         <v>8</v>
       </c>
@@ -1389,13 +1389,13 @@
       <c r="R17" s="1"/>
       <c r="S17" s="1"/>
       <c r="T17" s="1"/>
-      <c r="U17" s="15"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="17"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="26"/>
+      <c r="W17" s="26"/>
+      <c r="X17" s="27"/>
     </row>
     <row r="18" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="21" t="s">
         <v>48</v>
       </c>
       <c r="C18" s="6" t="s">
@@ -1420,13 +1420,13 @@
       <c r="R18" s="1"/>
       <c r="S18" s="1"/>
       <c r="T18" s="1"/>
-      <c r="U18" s="15"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="17"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="26"/>
+      <c r="W18" s="26"/>
+      <c r="X18" s="27"/>
     </row>
     <row r="19" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B19" s="8"/>
+      <c r="B19" s="21"/>
       <c r="C19" s="6" t="s">
         <v>8</v>
       </c>
@@ -1449,13 +1449,13 @@
       <c r="R19" s="1"/>
       <c r="S19" s="1"/>
       <c r="T19" s="1"/>
-      <c r="U19" s="15"/>
-      <c r="V19" s="16"/>
-      <c r="W19" s="16"/>
-      <c r="X19" s="17"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="26"/>
+      <c r="W19" s="26"/>
+      <c r="X19" s="27"/>
     </row>
     <row r="20" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="21" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="6" t="s">
@@ -1480,13 +1480,13 @@
       <c r="R20" s="1"/>
       <c r="S20" s="1"/>
       <c r="T20" s="1"/>
-      <c r="U20" s="18"/>
-      <c r="V20" s="19"/>
-      <c r="W20" s="19"/>
-      <c r="X20" s="20"/>
+      <c r="U20" s="28"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="30"/>
     </row>
     <row r="21" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B21" s="8"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="6" t="s">
         <v>8</v>
       </c>
@@ -1515,7 +1515,7 @@
       <c r="X21" s="1"/>
     </row>
     <row r="22" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="21" t="s">
         <v>44</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -1541,14 +1541,14 @@
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
-      <c r="V22" s="21" t="s">
+      <c r="V22" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="W22" s="22"/>
+      <c r="W22" s="32"/>
       <c r="X22" s="1"/>
     </row>
     <row r="23" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B23" s="8"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="6" t="s">
         <v>8</v>
       </c>
@@ -1572,31 +1572,31 @@
       <c r="S23" s="1"/>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
-      <c r="V23" s="23"/>
-      <c r="W23" s="24"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="34"/>
       <c r="X23" s="1"/>
     </row>
     <row r="24" spans="2:24" ht="15.75" customHeight="1">
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-      <c r="K24" s="10"/>
-      <c r="L24" s="10"/>
-      <c r="M24" s="10"/>
-      <c r="N24" s="10"/>
-      <c r="O24" s="10"/>
-      <c r="P24" s="10"/>
-      <c r="Q24" s="10"/>
-      <c r="R24" s="10"/>
-      <c r="S24" s="11"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
+      <c r="R24" s="19"/>
+      <c r="S24" s="20"/>
       <c r="T24" s="1"/>
       <c r="U24" s="1"/>
       <c r="V24" s="1"/>
@@ -1604,7 +1604,7 @@
       <c r="X24" s="1"/>
     </row>
     <row r="25" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C25" s="6" t="s">
@@ -1629,15 +1629,15 @@
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
       <c r="T25" s="1"/>
-      <c r="U25" s="12" t="s">
+      <c r="U25" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="V25" s="13"/>
-      <c r="W25" s="13"/>
-      <c r="X25" s="14"/>
+      <c r="V25" s="23"/>
+      <c r="W25" s="23"/>
+      <c r="X25" s="24"/>
     </row>
     <row r="26" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B26" s="8"/>
+      <c r="B26" s="21"/>
       <c r="C26" s="6" t="s">
         <v>8</v>
       </c>
@@ -1660,13 +1660,13 @@
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
-      <c r="U26" s="15"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="17"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="26"/>
+      <c r="W26" s="26"/>
+      <c r="X26" s="27"/>
     </row>
     <row r="27" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B27" s="33"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="6" t="s">
         <v>7</v>
       </c>
@@ -1689,13 +1689,13 @@
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
-      <c r="U27" s="15"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="17"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="26"/>
+      <c r="W27" s="26"/>
+      <c r="X27" s="27"/>
     </row>
     <row r="28" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B28" s="34"/>
+      <c r="B28" s="9"/>
       <c r="C28" s="6" t="s">
         <v>8</v>
       </c>
@@ -1718,13 +1718,13 @@
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
-      <c r="U28" s="15"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="17"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="26"/>
+      <c r="W28" s="26"/>
+      <c r="X28" s="27"/>
     </row>
     <row r="29" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B29" s="31"/>
+      <c r="B29" s="10"/>
       <c r="C29" s="6"/>
       <c r="D29" s="7"/>
       <c r="E29" s="1"/>
@@ -1743,13 +1743,13 @@
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
-      <c r="U29" s="15"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="17"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="26"/>
+      <c r="W29" s="26"/>
+      <c r="X29" s="27"/>
     </row>
     <row r="30" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B30" s="32"/>
+      <c r="B30" s="11"/>
       <c r="C30" s="6"/>
       <c r="D30" s="7"/>
       <c r="E30" s="1"/>
@@ -1768,13 +1768,13 @@
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
-      <c r="U30" s="15"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="17"/>
+      <c r="U30" s="25"/>
+      <c r="V30" s="26"/>
+      <c r="W30" s="26"/>
+      <c r="X30" s="27"/>
     </row>
     <row r="31" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="21" t="s">
         <v>42</v>
       </c>
       <c r="C31" s="6" t="s">
@@ -1799,13 +1799,13 @@
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
-      <c r="U31" s="18"/>
-      <c r="V31" s="19"/>
-      <c r="W31" s="19"/>
-      <c r="X31" s="20"/>
+      <c r="U31" s="28"/>
+      <c r="V31" s="29"/>
+      <c r="W31" s="29"/>
+      <c r="X31" s="30"/>
     </row>
     <row r="32" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B32" s="8"/>
+      <c r="B32" s="21"/>
       <c r="C32" s="6" t="s">
         <v>8</v>
       </c>
@@ -1834,7 +1834,7 @@
       <c r="X32" s="1"/>
     </row>
     <row r="33" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="21" t="s">
         <v>41</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -1860,14 +1860,14 @@
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
       <c r="U33" s="1"/>
-      <c r="V33" s="21" t="s">
+      <c r="V33" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="W33" s="22"/>
+      <c r="W33" s="32"/>
       <c r="X33" s="1"/>
     </row>
     <row r="34" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B34" s="8"/>
+      <c r="B34" s="21"/>
       <c r="C34" s="6" t="s">
         <v>8</v>
       </c>
@@ -1891,31 +1891,31 @@
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
       <c r="U34" s="1"/>
-      <c r="V34" s="23"/>
-      <c r="W34" s="24"/>
+      <c r="V34" s="33"/>
+      <c r="W34" s="34"/>
       <c r="X34" s="1"/>
     </row>
     <row r="35" spans="2:24" ht="15.75" customHeight="1">
-      <c r="B35" s="9" t="s">
+      <c r="B35" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="10"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="10"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="10"/>
-      <c r="H35" s="10"/>
-      <c r="I35" s="10"/>
-      <c r="J35" s="10"/>
-      <c r="K35" s="10"/>
-      <c r="L35" s="10"/>
-      <c r="M35" s="10"/>
-      <c r="N35" s="10"/>
-      <c r="O35" s="10"/>
-      <c r="P35" s="10"/>
-      <c r="Q35" s="10"/>
-      <c r="R35" s="10"/>
-      <c r="S35" s="11"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="19"/>
+      <c r="F35" s="19"/>
+      <c r="G35" s="19"/>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19"/>
+      <c r="K35" s="19"/>
+      <c r="L35" s="19"/>
+      <c r="M35" s="19"/>
+      <c r="N35" s="19"/>
+      <c r="O35" s="19"/>
+      <c r="P35" s="19"/>
+      <c r="Q35" s="19"/>
+      <c r="R35" s="19"/>
+      <c r="S35" s="20"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
@@ -1923,7 +1923,7 @@
       <c r="X35" s="1"/>
     </row>
     <row r="36" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="21" t="s">
         <v>14</v>
       </c>
       <c r="C36" s="6" t="s">
@@ -1948,15 +1948,15 @@
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
-      <c r="U36" s="12" t="s">
+      <c r="U36" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="V36" s="13"/>
-      <c r="W36" s="13"/>
-      <c r="X36" s="14"/>
+      <c r="V36" s="23"/>
+      <c r="W36" s="23"/>
+      <c r="X36" s="24"/>
     </row>
     <row r="37" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B37" s="8"/>
+      <c r="B37" s="21"/>
       <c r="C37" s="6" t="s">
         <v>8</v>
       </c>
@@ -1979,13 +1979,13 @@
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
-      <c r="U37" s="15"/>
-      <c r="V37" s="16"/>
-      <c r="W37" s="16"/>
-      <c r="X37" s="17"/>
+      <c r="U37" s="25"/>
+      <c r="V37" s="26"/>
+      <c r="W37" s="26"/>
+      <c r="X37" s="27"/>
     </row>
     <row r="38" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="21" t="s">
         <v>15</v>
       </c>
       <c r="C38" s="6" t="s">
@@ -2010,13 +2010,13 @@
       <c r="R38" s="3"/>
       <c r="S38" s="1"/>
       <c r="T38" s="1"/>
-      <c r="U38" s="15"/>
-      <c r="V38" s="16"/>
-      <c r="W38" s="16"/>
-      <c r="X38" s="17"/>
+      <c r="U38" s="25"/>
+      <c r="V38" s="26"/>
+      <c r="W38" s="26"/>
+      <c r="X38" s="27"/>
     </row>
     <row r="39" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B39" s="8"/>
+      <c r="B39" s="21"/>
       <c r="C39" s="6" t="s">
         <v>8</v>
       </c>
@@ -2039,13 +2039,13 @@
       <c r="R39" s="4"/>
       <c r="S39" s="1"/>
       <c r="T39" s="1"/>
-      <c r="U39" s="15"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="17"/>
+      <c r="U39" s="25"/>
+      <c r="V39" s="26"/>
+      <c r="W39" s="26"/>
+      <c r="X39" s="27"/>
     </row>
     <row r="40" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B40" s="8" t="s">
+      <c r="B40" s="21" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="6" t="s">
@@ -2070,13 +2070,13 @@
       <c r="R40" s="3"/>
       <c r="S40" s="1"/>
       <c r="T40" s="1"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="19"/>
-      <c r="W40" s="19"/>
-      <c r="X40" s="20"/>
+      <c r="U40" s="28"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="30"/>
     </row>
     <row r="41" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B41" s="8"/>
+      <c r="B41" s="21"/>
       <c r="C41" s="6" t="s">
         <v>8</v>
       </c>
@@ -2105,7 +2105,7 @@
       <c r="X41" s="1"/>
     </row>
     <row r="42" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B42" s="8" t="s">
+      <c r="B42" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C42" s="6" t="s">
@@ -2136,7 +2136,7 @@
       <c r="X42" s="1"/>
     </row>
     <row r="43" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B43" s="8"/>
+      <c r="B43" s="21"/>
       <c r="C43" s="6" t="s">
         <v>8</v>
       </c>
@@ -2165,26 +2165,26 @@
       <c r="X43" s="1"/>
     </row>
     <row r="44" spans="2:24" ht="14.25" customHeight="1">
-      <c r="B44" s="9" t="s">
+      <c r="B44" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C44" s="10"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="10"/>
-      <c r="F44" s="10"/>
-      <c r="G44" s="10"/>
-      <c r="H44" s="10"/>
-      <c r="I44" s="10"/>
-      <c r="J44" s="10"/>
-      <c r="K44" s="10"/>
-      <c r="L44" s="10"/>
-      <c r="M44" s="10"/>
-      <c r="N44" s="10"/>
-      <c r="O44" s="10"/>
-      <c r="P44" s="10"/>
-      <c r="Q44" s="10"/>
-      <c r="R44" s="10"/>
-      <c r="S44" s="11"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="19"/>
+      <c r="G44" s="19"/>
+      <c r="H44" s="19"/>
+      <c r="I44" s="19"/>
+      <c r="J44" s="19"/>
+      <c r="K44" s="19"/>
+      <c r="L44" s="19"/>
+      <c r="M44" s="19"/>
+      <c r="N44" s="19"/>
+      <c r="O44" s="19"/>
+      <c r="P44" s="19"/>
+      <c r="Q44" s="19"/>
+      <c r="R44" s="19"/>
+      <c r="S44" s="20"/>
       <c r="T44" s="1"/>
       <c r="U44" s="1"/>
       <c r="V44" s="1"/>
@@ -2218,21 +2218,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B2:S3"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="B6:S6"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="B22:B23"/>
-    <mergeCell ref="B24:S24"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="B13:S13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="B18:B19"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="B42:B43"/>
     <mergeCell ref="B44:S44"/>
@@ -2249,6 +2234,21 @@
     <mergeCell ref="B36:B37"/>
     <mergeCell ref="B38:B39"/>
     <mergeCell ref="B20:B21"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B2:S3"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="B6:S6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="B22:B23"/>
+    <mergeCell ref="B24:S24"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="B13:S13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="B18:B19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
